--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
   <si>
     <t>!Table</t>
   </si>
@@ -425,6 +425,20 @@
   <si>
     <t>업적 달성</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimControllerName</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_Melee</t>
+  </si>
+  <si>
+    <t>AOC_Hero_Range</t>
   </si>
 </sst>
 </file>
@@ -672,7 +686,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -753,6 +767,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1029,7 +1049,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1148,25 +1168,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="5" max="6" width="19.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1">
+    <row r="1" spans="1:12" s="4" customFormat="1">
       <c r="A1" s="20" t="s">
         <v>58</v>
       </c>
@@ -1174,7 +1194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="5"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1189,25 +1209,28 @@
         <v>74</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
         <v>16</v>
@@ -1222,16 +1245,16 @@
         <v>73</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>2</v>
@@ -1239,8 +1262,11 @@
       <c r="K3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1253,26 +1279,29 @@
       <c r="E4" t="s">
         <v>68</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" t="s">
         <v>53</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>10</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="8">
         <v>6</v>
       </c>
-      <c r="J4" s="8">
+      <c r="K4" s="8">
         <v>4</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1285,26 +1314,29 @@
       <c r="E5" t="s">
         <v>68</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" t="s">
         <v>54</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1E-3</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="I5" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="8">
+      <c r="J5" s="8">
         <v>6</v>
       </c>
-      <c r="J5" s="8">
+      <c r="K5" s="8">
         <v>4</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1317,26 +1349,29 @@
       <c r="E6" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" t="s">
         <v>55</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1E-3</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="I6" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="8">
+      <c r="J6" s="8">
         <v>6</v>
       </c>
-      <c r="J6" s="8">
+      <c r="K6" s="8">
         <v>4</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>301</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1349,70 +1384,73 @@
       <c r="E7" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" t="s">
         <v>52</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.02</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="I7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="8">
         <v>6</v>
       </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
         <v>4</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="F11"/>
-      <c r="G11" s="26"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="F12"/>
-      <c r="G12" s="26"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="F13"/>
-      <c r="G13" s="26"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="F14"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="G15" s="26"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="G16" s="26"/>
-    </row>
-    <row r="17" spans="6:8">
-      <c r="F17" s="8"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="6:8">
-      <c r="F18" s="8"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="6:8">
-      <c r="F19" s="8"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="6:8">
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21" spans="6:8">
-      <c r="G21" s="26"/>
-    </row>
-    <row r="22" spans="6:8">
-      <c r="G22" s="26"/>
+    <row r="11" spans="1:12">
+      <c r="G11"/>
+      <c r="H11" s="26"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="G12"/>
+      <c r="H12" s="26"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="G13"/>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="G14"/>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16" s="26"/>
+    </row>
+    <row r="17" spans="7:9">
+      <c r="G17" s="8"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="7:9">
+      <c r="G18" s="8"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="7:9">
+      <c r="G19" s="8"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="7:9">
+      <c r="H20" s="26"/>
+    </row>
+    <row r="21" spans="7:9">
+      <c r="H21" s="26"/>
+    </row>
+    <row r="22" spans="7:9">
+      <c r="H22" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t>!Table</t>
   </si>
@@ -112,10 +112,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>양손검</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>룬검</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -129,26 +125,6 @@
   </si>
   <si>
     <t>WeaponType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_DualPistols</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_CrossBow</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_RuneSword</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_GreatSword</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Greatsword</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -375,10 +351,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_GreatSword_Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_RuneSword_Attack</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -435,10 +407,48 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>AOC_Hero_Melee</t>
-  </si>
-  <si>
-    <t>AOC_Hero_Range</t>
+    <t>DualBlades</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍검</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Attack</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_DualBlades</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_RuneSword</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_CrossBow</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_DualPistols</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_CrossBow</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_DualBlades</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_DualPistols</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_RuneSword</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1072,27 +1082,27 @@
   <sheetData>
     <row r="1" spans="1:3" s="18" customFormat="1">
       <c r="A1" s="21" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3">
       <c r="B2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="B3" s="25" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1101,35 +1111,35 @@
     </row>
     <row r="5" spans="1:3" s="18" customFormat="1">
       <c r="A5" s="21" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5" s="23"/>
     </row>
     <row r="6" spans="1:3">
       <c r="B6" s="26" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" s="26" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" s="26" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1175,7 +1185,8 @@
     <col min="2" max="2" width="19.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
@@ -1188,10 +1199,10 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1">
       <c r="A1" s="20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1203,31 +1214,31 @@
         <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1239,22 +1250,22 @@
         <v>3</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>2</v>
@@ -1268,28 +1279,28 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J4" s="8">
         <v>6</v>
@@ -1303,28 +1314,28 @@
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H5">
         <v>1E-3</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J5" s="8">
         <v>6</v>
@@ -1338,28 +1349,28 @@
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H6">
         <v>1E-3</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="J6" s="8">
         <v>6</v>
@@ -1373,28 +1384,28 @@
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H7">
         <v>0.02</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J7" s="8">
         <v>6</v>
@@ -1486,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="10"/>
@@ -1511,7 +1522,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>6</v>
@@ -1520,19 +1531,19 @@
         <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -1560,10 +1571,10 @@
         <v>12</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>14</v>
@@ -1572,7 +1583,7 @@
         <v>14</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1747,10 +1758,10 @@
   <sheetData>
     <row r="1" spans="1:13" s="4" customFormat="1">
       <c r="A1" s="20" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1765,16 +1776,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H2" s="8"/>
       <c r="J2" s="8"/>
@@ -1785,74 +1796,74 @@
     <row r="3" spans="1:13">
       <c r="A3" s="5"/>
       <c r="B3" s="14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H3" s="8"/>
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E4" s="11" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G4"/>
     </row>
     <row r="5" spans="1:13">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E5" s="11" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G5"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G6"/>
     </row>
@@ -2038,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2047,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
@@ -2056,10 +2067,10 @@
     <row r="3" spans="1:10">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
   <si>
     <t>!Table</t>
   </si>
@@ -448,6 +448,18 @@
   </si>
   <si>
     <t>AOC_Hero_RuneSword</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dev_SkillIDs</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Skill</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1178,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
@@ -1193,11 +1205,11 @@
     <col min="10" max="10" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1">
+    <row r="1" spans="1:13" s="4" customFormat="1">
       <c r="A1" s="20" t="s">
         <v>52</v>
       </c>
@@ -1205,7 +1217,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="5"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1240,8 +1252,11 @@
       <c r="L2" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
         <v>16</v>
@@ -1276,8 +1291,11 @@
       <c r="L3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="B4" s="1" t="s">
         <v>88</v>
       </c>
@@ -1297,7 +1315,7 @@
         <v>47</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I4" s="26" t="s">
         <v>87</v>
@@ -1311,8 +1329,11 @@
       <c r="L4" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5" s="1" t="s">
         <v>89</v>
       </c>
@@ -1347,7 +1368,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="B6" s="1" t="s">
         <v>90</v>
       </c>
@@ -1382,7 +1403,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="B7" s="1" t="s">
         <v>91</v>
       </c>
@@ -1417,26 +1438,26 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="G11"/>
       <c r="H11" s="26"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="G12"/>
       <c r="H12" s="26"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="G13"/>
       <c r="H13" s="26"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="G14"/>
       <c r="H14" s="26"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="H15" s="26"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="H16" s="26"/>
     </row>
     <row r="17" spans="7:9">

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="26" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="#SkillTreeNode" sheetId="19" r:id="rId3"/>
     <sheet name="#SkillPoint" sheetId="25" r:id="rId4"/>
     <sheet name="#MasteryLevelExp" sheetId="21" r:id="rId5"/>
+    <sheet name="#MasteryLevelBonus" sheetId="27" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="168">
   <si>
     <t>!Table</t>
   </si>
@@ -43,37 +44,34 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
   </si>
   <si>
-    <t>NodePos_Column</t>
-  </si>
-  <si>
     <t>Name</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -89,166 +87,138 @@
       </rPr>
       <t>roupID</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>PrevNodeID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Option</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!WeaponMastery</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>룬검</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>석궁</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>쌍권총</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>WeaponType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>RuneSword</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>CrossBow</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>DualPistols</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillTreeNode</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>TotalExperience</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MasteryLevelExp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Level</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Item</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Achievement</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MaxPoint</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>업적 달성</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>레벨업시 획득</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillTreeNodeGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxRow</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxColumn</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!SkillPoint</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequireTreePoint</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>BaseValue</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>PerLevelValue</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MaxLevel</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_DAMAGE_ADD</t>
   </si>
   <si>
     <t>OPT_ATK_ADD</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>OPT_ATK_SPEED_ADD</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_RATE_ADD</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>NodePos_Row</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!Option</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -276,203 +246,485 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>IsShared</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>지식의서 소모</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Skill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalAttackSkill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Enum</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Melee</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거리</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponRangeType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!WeaponRangeType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>RangeType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!WeaponType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponMastery</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RuneSword_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_CrossBow_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_DualPistols_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>SourceType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPointSourceType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MasteryLevel</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Achievement</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillPointSourceType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>마스터리 레벨업</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬포인트 아이템</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 달성</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimControllerName</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlades</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌍검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_DualBlades</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_RuneSword</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_CrossBow</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_DualPistols</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_CrossBow</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_DualBlades</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_DualPistols</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_RuneSword</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dev_SkillIDs</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Skill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Table</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_MAX_HP_ADD</t>
+  </si>
+  <si>
+    <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_ATK_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_ATK_SPEED_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_CRIT_RATE_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
+  </si>
+  <si>
+    <t>OPT_BOSS_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>OPT_DEF_PEN_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MAX_HP_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_HP_REGEN_ADD</t>
+  </si>
+  <si>
+    <t>OPT_DEF_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_DAMAGE_REDUCTION_ADD</t>
+  </si>
+  <si>
+    <t>OPT_LIFE_ON_HIT_ADD</t>
+  </si>
+  <si>
+    <t>OPT_EVASION_RATE_ADD</t>
+  </si>
+  <si>
+    <t>OPT_BLOCK_RATE_ADD</t>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>TypeIcon_Weapon</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusOption</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusPerLevel</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Skill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalAttackSkill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Enum</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranged</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>근거리</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponRangeType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!WeaponRangeType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RangeType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!WeaponType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponMastery</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_RuneSword_Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_CrossBow_Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_DualPistols_Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SourceType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillPointSourceType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MasteryLevel</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Achievement</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillPointSourceType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>마스터리 레벨업</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬포인트 아이템</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>업적 달성</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MasteryLevelBonus</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelBonusOption</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelBonusPerLevel</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillTreeNodeGroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>NodePos_Column</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxRow</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxColumn</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>AnimControllerName</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>DualBlades</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>쌍검</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_DualBlades</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_RuneSword</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_CrossBow</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mastery_DualPistols</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_CrossBow</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_DualBlades</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_DualPistols</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_RuneSword</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dev_SkillIDs</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Skill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_001</t>
+  </si>
+  <si>
+    <t>skill_002</t>
+  </si>
+  <si>
+    <t>skill_003</t>
+  </si>
+  <si>
+    <t>skill_004</t>
+  </si>
+  <si>
+    <t>skill_005</t>
+  </si>
+  <si>
+    <t>skill_006</t>
+  </si>
+  <si>
+    <t>skill_007</t>
+  </si>
+  <si>
+    <t>skill_008</t>
+  </si>
+  <si>
+    <t>skill_009</t>
+  </si>
+  <si>
+    <t>skill_010</t>
+  </si>
+  <si>
+    <t>skill_011</t>
+  </si>
+  <si>
+    <t>skill_012</t>
+  </si>
+  <si>
+    <t>skill_013</t>
+  </si>
+  <si>
+    <t>skill_014</t>
+  </si>
+  <si>
+    <t>skill_015</t>
+  </si>
+  <si>
+    <t>skill_016</t>
+  </si>
+  <si>
+    <t>skill_017</t>
+  </si>
+  <si>
+    <t>skill_018</t>
+  </si>
+  <si>
+    <t>PrevNodeID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>노드1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>노드2</t>
+  </si>
+  <si>
+    <t>노드3</t>
+  </si>
+  <si>
+    <t>노드4</t>
+  </si>
+  <si>
+    <t>노드5</t>
+  </si>
+  <si>
+    <t>노드6</t>
+  </si>
+  <si>
+    <t>노드7</t>
+  </si>
+  <si>
+    <t>노드8</t>
+  </si>
+  <si>
+    <t>노드9</t>
+  </si>
+  <si>
+    <t>노드10</t>
+  </si>
+  <si>
+    <t>노드11</t>
+  </si>
+  <si>
+    <t>노드12</t>
+  </si>
+  <si>
+    <t>노드13</t>
+  </si>
+  <si>
+    <t>노드14</t>
+  </si>
+  <si>
+    <t>노드15</t>
+  </si>
+  <si>
+    <t>노드16</t>
+  </si>
+  <si>
+    <t>노드17</t>
+  </si>
+  <si>
+    <t>노드18</t>
+  </si>
+  <si>
+    <t>NodePos_Row</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillTreeNode</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireTreePoint</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -700,100 +952,106 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1071,7 +1329,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1083,8 +1341,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.625" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.625" style="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="1" bestFit="1" customWidth="1"/>
@@ -1092,76 +1350,76 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="18" customFormat="1">
-      <c r="A1" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="23"/>
+    <row r="1" spans="1:3" s="17" customFormat="1">
+      <c r="A1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3">
       <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="B3" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="24" t="s">
+      <c r="B3" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="24"/>
+      <c r="C4" s="23"/>
+    </row>
+    <row r="5" spans="1:3" s="17" customFormat="1">
+      <c r="A5" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" s="25"/>
-      <c r="C4" s="24"/>
-    </row>
-    <row r="5" spans="1:3" s="18" customFormat="1">
-      <c r="A5" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="B6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>80</v>
+      <c r="B6" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="B7" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>81</v>
+      <c r="B7" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="B8" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>82</v>
+      <c r="B8" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="C9" s="24"/>
+      <c r="C9" s="23"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="C10" s="24"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="C11" s="24"/>
+      <c r="C11" s="23"/>
     </row>
     <row r="12" spans="1:3">
       <c r="C12" s="1"/>
@@ -1176,48 +1434,49 @@
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="1"/>
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1">
-      <c r="A1" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    <row r="1" spans="1:14" s="4" customFormat="1">
+      <c r="A1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="5"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1226,64 +1485,67 @@
         <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>36</v>
+        <v>116</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>117</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>2</v>
@@ -1292,200 +1554,215 @@
         <v>2</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="B4" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="8">
+        <v>6</v>
+      </c>
+      <c r="L4" s="8">
+        <v>4</v>
+      </c>
+      <c r="M4" s="1">
+        <v>101</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="8">
+        <v>6</v>
+      </c>
+      <c r="L5" s="8">
+        <v>4</v>
+      </c>
+      <c r="M5" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="K6" s="8">
         <v>6</v>
       </c>
-      <c r="K4" s="8">
+      <c r="L6" s="8">
         <v>4</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M6" s="1">
         <v>101</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="B5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5">
-        <v>1E-3</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="8">
+      <c r="F7" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>0.02</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="8">
         <v>6</v>
       </c>
-      <c r="K5" s="8">
+      <c r="L7" s="8">
         <v>4</v>
       </c>
-      <c r="L5" s="1">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="B6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6">
-        <v>1E-3</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="8">
-        <v>6</v>
-      </c>
-      <c r="K6" s="8">
-        <v>4</v>
-      </c>
-      <c r="L6" s="1">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7">
-        <v>0.02</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="8">
-        <v>6</v>
-      </c>
-      <c r="K7" s="8">
-        <v>4</v>
-      </c>
-      <c r="L7" s="1">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="G11"/>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="G12"/>
-      <c r="H12" s="26"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="G13"/>
-      <c r="H13" s="26"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="G14"/>
-      <c r="H14" s="26"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="H15" s="26"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="H16" s="26"/>
-    </row>
-    <row r="17" spans="7:9">
-      <c r="G17" s="8"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="7:9">
-      <c r="G18" s="8"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="7:9">
-      <c r="G19" s="8"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="7:9">
-      <c r="H20" s="26"/>
-    </row>
-    <row r="21" spans="7:9">
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="7:9">
-      <c r="H22" s="26"/>
+      <c r="M7" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="H11"/>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="H12"/>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="H13"/>
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="H14"/>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" s="8"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="8:10">
+      <c r="H18" s="8"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="8:10">
+      <c r="H19" s="8"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="8:10">
+      <c r="I20" s="25"/>
+    </row>
+    <row r="21" spans="8:10">
+      <c r="I21" s="25"/>
+    </row>
+    <row r="22" spans="8:10">
+      <c r="I22" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1493,32 +1770,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
     <col min="2" max="2" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="7.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.25" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1">
+    <row r="1" spans="1:15" s="4" customFormat="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>24</v>
+      <c r="B1" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="10"/>
@@ -1527,231 +1805,851 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="5"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="9"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="9"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="M3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>101</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11">
+        <v>1</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="11">
+        <v>2</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>101</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="1">
+        <v>5</v>
+      </c>
+      <c r="M5" s="1">
+        <v>2</v>
+      </c>
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>101</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="11">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="1">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>101</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="11">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1">
+        <v>3</v>
+      </c>
+      <c r="N7" s="11">
+        <v>3</v>
+      </c>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>101</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="N8" s="11">
+        <v>5</v>
+      </c>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>101</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="11">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="N9" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>101</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>101</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>15</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="M11" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="1">
         <v>9</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="C12" s="1">
+        <v>101</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="11">
+        <v>4</v>
+      </c>
+      <c r="I12" s="1">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1">
+        <v>15</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="N12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="1">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="C13" s="1">
+        <v>101</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>7</v>
+      </c>
+      <c r="J13" s="1">
+        <v>25</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="8">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <v>101</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4</v>
+      </c>
+      <c r="H14" s="11">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>25</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="L14" s="11">
+        <v>50</v>
+      </c>
+      <c r="M14" s="11">
+        <v>20</v>
+      </c>
+      <c r="N14" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1">
+        <v>101</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4</v>
+      </c>
+      <c r="H15" s="11">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1">
+        <v>25</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="11">
+        <v>5</v>
+      </c>
+      <c r="M15" s="11">
+        <v>5</v>
+      </c>
+      <c r="N15" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="1">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>101</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J16" s="1">
+        <v>40</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="L16" s="11">
+        <v>10</v>
+      </c>
+      <c r="M16" s="11">
+        <v>2</v>
+      </c>
+      <c r="N16" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="1">
+        <v>14</v>
+      </c>
+      <c r="C17" s="1">
+        <v>101</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>11</v>
+      </c>
+      <c r="J17" s="1">
+        <v>40</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="N17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="1">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1">
+        <v>101</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="11">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1">
         <v>12</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="J18" s="1">
+        <v>40</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="1">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>101</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="11">
+        <v>4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>40</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="N19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="1">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1">
+        <v>101</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="1">
+        <v>6</v>
+      </c>
+      <c r="H20" s="11">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1">
         <v>14</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="F4" s="8"/>
-      <c r="G4" s="11"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="F5" s="8"/>
-      <c r="G5" s="11"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="F6" s="8"/>
-      <c r="G6" s="11"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="G9" s="11"/>
-      <c r="K9" s="8"/>
-      <c r="N9" s="8"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="G10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-    </row>
-    <row r="17" spans="6:13">
-      <c r="G17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-    </row>
-    <row r="18" spans="6:13">
-      <c r="G18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-    </row>
-    <row r="20" spans="6:13">
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" spans="6:13">
-      <c r="G21" s="11"/>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="6:13">
-      <c r="G22" s="11"/>
-      <c r="K22" s="11"/>
+      <c r="J20" s="1">
+        <v>55</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="N20" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="1">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1">
+        <v>101</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="8">
+        <v>6</v>
+      </c>
+      <c r="H21" s="1">
+        <v>3</v>
+      </c>
+      <c r="I21" s="1">
+        <v>15</v>
+      </c>
+      <c r="J21" s="1">
+        <v>55</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="M21" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="N21" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="G22" s="8"/>
+      <c r="H22" s="11"/>
+      <c r="K22" s="25"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
-    </row>
-    <row r="23" spans="6:13">
-      <c r="F23" s="8"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-    </row>
-    <row r="24" spans="6:13">
-      <c r="F24" s="8"/>
-      <c r="G24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-    </row>
-    <row r="25" spans="6:13">
-      <c r="G25" s="11"/>
-    </row>
-    <row r="26" spans="6:13">
-      <c r="G26" s="11"/>
-    </row>
-    <row r="27" spans="6:13">
-      <c r="F27" s="8"/>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="6:13">
-      <c r="F28" s="8"/>
-      <c r="G28" s="11"/>
-    </row>
-    <row r="29" spans="6:13">
-      <c r="G29" s="11"/>
-    </row>
-    <row r="30" spans="6:13">
-      <c r="G30" s="11"/>
-    </row>
-    <row r="31" spans="6:13">
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="6:13">
-      <c r="F32" s="8"/>
-      <c r="G32" s="11"/>
-    </row>
-    <row r="33" spans="6:7">
-      <c r="G33" s="11"/>
-    </row>
-    <row r="34" spans="6:7">
-      <c r="G34" s="11"/>
-    </row>
-    <row r="35" spans="6:7">
-      <c r="F35" s="8"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="H23" s="11"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="H24" s="11"/>
+      <c r="K24" s="25"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="G25" s="8"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="G26" s="8"/>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="G30" s="8"/>
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="H32" s="11"/>
+    </row>
+    <row r="33" spans="7:7">
+      <c r="G33" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1778,11 +2676,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="4" customFormat="1">
-      <c r="A1" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>39</v>
+      <c r="A1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1797,16 +2695,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H2" s="8"/>
       <c r="J2" s="8"/>
@@ -1817,74 +2715,74 @@
     <row r="3" spans="1:13">
       <c r="A3" s="5"/>
       <c r="B3" s="14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H3" s="8"/>
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>76</v>
+      <c r="F4" s="25" t="s">
+        <v>66</v>
       </c>
       <c r="G4"/>
     </row>
     <row r="5" spans="1:13">
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E5" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>77</v>
+      <c r="F5" s="25" t="s">
+        <v>67</v>
       </c>
       <c r="G5"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E6" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>78</v>
+      <c r="F6" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="G6"/>
     </row>
@@ -1907,7 +2805,7 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="28"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:13">
       <c r="C10"/>
@@ -2039,7 +2937,7 @@
       <c r="I35" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2069,8 +2967,8 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>27</v>
+      <c r="B1" s="15" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2079,22 +2977,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+        <v>23</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:10">
@@ -4513,7 +5411,129 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="4" customFormat="1">
+      <c r="A1" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5"/>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5"/>
+      <c r="B3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="C7"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="C11"/>
+      <c r="D11" s="25"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="C12"/>
+      <c r="D12" s="25"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13"/>
+      <c r="D13" s="25"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14"/>
+      <c r="D14" s="25"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="D15" s="25"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="D16" s="25"/>
+    </row>
+    <row r="17" spans="3:4">
+      <c r="C17" s="8"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="3:4">
+      <c r="C18" s="8"/>
+      <c r="D18" s="25"/>
+    </row>
+    <row r="19" spans="3:4">
+      <c r="C19" s="8"/>
+      <c r="D19" s="25"/>
+    </row>
+    <row r="20" spans="3:4">
+      <c r="D20" s="25"/>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="D21" s="25"/>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="D22" s="25"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
